--- a/tasks/HR_Troutly_T1v2_august_operating_review/05_rubric_import.xlsx
+++ b/tasks/HR_Troutly_T1v2_august_operating_review/05_rubric_import.xlsx
@@ -546,7 +546,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/operating_review_request.pdf", "index": null, "source": "task", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/operating_review_request.pdf", "index": null, "source": "task", "snapshotId": "snap_fbf9dc06005743a28e8d6fd2238c7f5f", "transformations": []}]</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/operating_review_request.pdf", "index": null, "source": "task", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/operating_review_request.pdf", "index": null, "source": "task", "snapshotId": "snap_fbf9dc06005743a28e8d6fd2238c7f5f", "transformations": []}]</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/operating_review_request.pdf", "index": null, "source": "task", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/operating_review_request.pdf", "index": null, "source": "task", "snapshotId": "snap_fbf9dc06005743a28e8d6fd2238c7f5f", "transformations": []}]</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/operating_review_request.pdf", "index": null, "source": "task", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/Recruiting/ATS_Requisition_Export_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/operating_review_request.pdf", "index": null, "source": "task", "snapshotId": "snap_fbf9dc06005743a28e8d6fd2238c7f5f", "transformations": []}, {"name": "filesystem/Recruiting/ATS_Requisition_Export_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
